--- a/DataRepo/data/tests/study_doc_versions/consolidated.xlsx
+++ b/DataRepo/data/tests/study_doc_versions/consolidated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/study_doc_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4776D2F3-5119-4E4C-B92F-5F208DCBD032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF23DE4-0AFA-EE4E-8FA6-6D6492F0ACC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15620" yWindow="6600" windowWidth="26840" windowHeight="15940" activeTab="1" xr2:uid="{26BF4920-AA5B-7041-9D13-F7650B478138}"/>
+    <workbookView xWindow="15620" yWindow="6600" windowWidth="26840" windowHeight="15940" activeTab="5" xr2:uid="{26BF4920-AA5B-7041-9D13-F7650B478138}"/>
   </bookViews>
   <sheets>
     <sheet name="Treatments" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="195">
   <si>
     <t>Animal Treatment</t>
   </si>
@@ -52,12 +52,6 @@
     <t>no treatment</t>
   </si>
   <si>
-    <t>No treatment was applied to the animal.  Animal was maintained on normal diet (LabDiet #5053 "Maintenance"), housed at room temperature with a normal light cycle.</t>
-  </si>
-  <si>
-    <t>TraceBase Tissue Name</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -214,9 +208,6 @@
     <t>testicle</t>
   </si>
   <si>
-    <t>testical</t>
-  </si>
-  <si>
     <t>ovary</t>
   </si>
   <si>
@@ -226,9 +217,6 @@
     <t>tumor_nonspecific</t>
   </si>
   <si>
-    <t>nonspecified tumor - only use this if other information is unknown</t>
-  </si>
-  <si>
     <t>tumor_hct116</t>
   </si>
   <si>
@@ -259,9 +247,6 @@
     <t>BCAAs (VLI)</t>
   </si>
   <si>
-    <t>BCAAs (VLI) {valine-[13C5,15N1]; leucine-[13C6,15N1]; isoleucine-[13C6,15N1]}</t>
-  </si>
-  <si>
     <t>valine-[13C5,15N1]</t>
   </si>
   <si>
@@ -496,9 +481,6 @@
     <t>Polar HILIC is the way to go!</t>
   </si>
   <si>
-    <t>6EAAs (MFWKHT) {methionine-[13C5]; phenylalanine-[13C9]; tryptophan-[13C11]; lysine-[13C6]; histidine-[13C6]; threonine-[13C4]}</t>
-  </si>
-  <si>
     <t>methionine-[13C5]</t>
   </si>
   <si>
@@ -590,6 +572,60 @@
   </si>
   <si>
     <t>6EAAs (MFWKHT)</t>
+  </si>
+  <si>
+    <t>glutamine-[13C5,15N2][200]</t>
+  </si>
+  <si>
+    <t>alanine-[13C3,15N1][180]</t>
+  </si>
+  <si>
+    <t>BCAAs (VLI) {valine-[13C5,15N1][20]; leucine-[13C6,15N1][24]; isoleucine-[13C6,15N1][12]}</t>
+  </si>
+  <si>
+    <t>6EAAs (MFWKHT) {methionine-[13C5][14]; phenylalanine-[13C9][18]; tryptophan-[13C11][5]; lysine-[13C6][23]; histidine-[13C6][10]; threonine-[13C4][15]}</t>
+  </si>
+  <si>
+    <t>feces</t>
+  </si>
+  <si>
+    <t>poop shmeer</t>
+  </si>
+  <si>
+    <t>Tissue</t>
+  </si>
+  <si>
+    <t>no manipulation besides what is already described in other fields</t>
+  </si>
+  <si>
+    <t>unspecified tumor - only use this if other information is unknown</t>
+  </si>
+  <si>
+    <t>C5H11NO2</t>
+  </si>
+  <si>
+    <t>HMDB0000883</t>
+  </si>
+  <si>
+    <t>L-Valine</t>
+  </si>
+  <si>
+    <t>C6H13NO2</t>
+  </si>
+  <si>
+    <t>HMDB0000687</t>
+  </si>
+  <si>
+    <t>leu</t>
+  </si>
+  <si>
+    <t>HMDB0000172</t>
+  </si>
+  <si>
+    <t>L-Isoleucine</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
 </sst>
 </file>
@@ -679,7 +715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -698,6 +734,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,7 +1074,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="137.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1053,7 +1090,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1075,10 +1112,10 @@
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -1102,298 +1139,305 @@
     </row>
     <row r="2" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="7"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D11" s="7"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
     <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2372,25 +2416,25 @@
     <col min="2" max="2" width="18.5" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="109.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="124.1640625" style="5" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
@@ -2407,13 +2451,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5">
         <v>200</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.2">
@@ -2421,13 +2465,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D3" s="5">
         <v>180</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.15">
@@ -2435,16 +2479,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D4" s="5">
         <v>20</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.15">
@@ -2452,16 +2496,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" s="5">
         <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.15">
@@ -2469,16 +2513,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5">
         <v>12</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2486,16 +2530,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D7" s="5">
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2503,16 +2547,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D8" s="5">
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2520,16 +2564,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
       <c r="E9" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2537,16 +2581,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D10" s="5">
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2554,16 +2598,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D11" s="5">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
@@ -2571,16 +2615,16 @@
         <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D12" s="5">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2605,25 +2649,25 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="G1" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -2634,10 +2678,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D2" s="5">
         <v>13</v>
@@ -2646,7 +2690,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -2654,10 +2698,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D3" s="5">
         <v>15</v>
@@ -2666,7 +2710,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -2674,10 +2718,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D4" s="5">
         <v>13</v>
@@ -2686,7 +2730,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
@@ -2694,10 +2738,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D5" s="5">
         <v>15</v>
@@ -2706,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.15">
@@ -2714,10 +2758,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D6" s="5">
         <v>13</v>
@@ -2726,7 +2770,7 @@
         <v>5</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
@@ -2734,10 +2778,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="5">
         <v>15</v>
@@ -2746,7 +2790,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.15">
@@ -2754,10 +2798,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D8" s="5">
         <v>13</v>
@@ -2766,7 +2810,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
@@ -2774,10 +2818,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D9" s="5">
         <v>15</v>
@@ -2786,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.15">
@@ -2794,10 +2838,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D10" s="5">
         <v>13</v>
@@ -2806,7 +2850,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.15">
@@ -2814,10 +2858,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D11" s="5">
         <v>15</v>
@@ -2826,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.15">
@@ -2834,10 +2878,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D12" s="5">
         <v>13</v>
@@ -2846,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.15">
@@ -2854,10 +2898,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D13" s="5">
         <v>13</v>
@@ -2866,7 +2910,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.15">
@@ -2874,10 +2918,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D14" s="5">
         <v>13</v>
@@ -2886,7 +2930,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.15">
@@ -2894,10 +2938,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D15" s="5">
         <v>13</v>
@@ -2906,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.15">
@@ -2914,10 +2958,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D16" s="5">
         <v>13</v>
@@ -2926,7 +2970,7 @@
         <v>6</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
@@ -2934,10 +2978,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D17" s="5">
         <v>13</v>
@@ -2946,7 +2990,7 @@
         <v>4</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.2">
@@ -2962,11 +3006,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43C64185-A3B1-C641-950F-9993BD5B86E1}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="5" customWidth="1"/>
     <col min="3" max="3" width="13" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="98.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="5"/>
@@ -2974,16 +3018,16 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
@@ -2996,279 +3040,321 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>164</v>
-      </c>
       <c r="C16" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3290,34 +3376,42 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="12" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C2" s="5">
         <v>25</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="D3" s="13"/>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.15">
+      <c r="A3" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="D4" s="13"/>
